--- a/Components/componentes_completados_6.xlsx
+++ b/Components/componentes_completados_6.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B38"/>
+  <dimension ref="A1:D38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -440,375 +440,535 @@
           <t>MouserPartNumber</t>
         </is>
       </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>PCB NUM</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>COMPONENTS PER PCB</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>5</v>
+        <v>1000</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>71-CRCW0805-270-E3</t>
         </is>
+      </c>
+      <c r="C2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>10</v>
+        <v>2000</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
           <t>71-RCS08051M00JNEA</t>
         </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>10</v>
+        <v>2000</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
           <t>71-CRCW0805100KJNECC</t>
         </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>10</v>
+        <v>2000</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
           <t>71-CRCW0805-330-E3</t>
         </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>15</v>
+        <v>3000</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
           <t>71-CRCW080510R0FKEC</t>
         </is>
+      </c>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>45</v>
+        <v>9000</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
           <t>71-CRCW0805103JT-RT6</t>
         </is>
+      </c>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="n">
+        <v>9</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>35</v>
+        <v>7000</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
           <t>594-RCA08050000ZSEC</t>
         </is>
+      </c>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>5</v>
+        <v>1000</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
           <t>523-GSB4D313302Y1HR</t>
         </is>
+      </c>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>5</v>
+        <v>1000</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
           <t>926-LM1117IMPX33NOPB</t>
         </is>
+      </c>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>5</v>
+        <v>1000</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
           <t>595-TPS63060DSCT</t>
         </is>
+      </c>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>5</v>
+        <v>1000</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
           <t>755-RB058L-30DDTE25</t>
         </is>
+      </c>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>5</v>
+        <v>1000</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
           <t>652-SRP6530A-1R0M</t>
         </is>
+      </c>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>5</v>
+        <v>1000</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
           <t>852-PC817X4NSZ1B</t>
         </is>
+      </c>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>5</v>
+        <v>1000</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
           <t>895-FT234XD-R</t>
         </is>
+      </c>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>10</v>
+        <v>2000</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
           <t>70-ILSB0805ER1R0K</t>
         </is>
+      </c>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>10</v>
+        <v>2000</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
           <t>595-TLV9062IDR</t>
         </is>
+      </c>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>5</v>
+        <v>1000</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
           <t>179-SJ3-35094BG</t>
         </is>
+      </c>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>5</v>
+        <v>1000</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
           <t>356-ESP32WRVE26464PC</t>
         </is>
+      </c>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>10</v>
+        <v>2000</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
           <t>583-BC817</t>
         </is>
+      </c>
+      <c r="C20" t="inlineStr"/>
+      <c r="D20" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>10</v>
+        <v>2000</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
           <t>583-BC807</t>
         </is>
+      </c>
+      <c r="C21" t="inlineStr"/>
+      <c r="D21" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>5</v>
+        <v>1000</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
           <t>942-IRF3205ZPBF</t>
         </is>
+      </c>
+      <c r="C22" t="inlineStr"/>
+      <c r="D22" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>10</v>
+        <v>2000</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
           <t>757-TTA006BQ</t>
         </is>
+      </c>
+      <c r="C23" t="inlineStr"/>
+      <c r="D23" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>10</v>
+        <v>2000</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
           <t>757-TTC011BQ</t>
         </is>
+      </c>
+      <c r="C24" t="inlineStr"/>
+      <c r="D24" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>30</v>
+        <v>6000</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
           <t>710-885342207014</t>
         </is>
+      </c>
+      <c r="C25" t="inlineStr"/>
+      <c r="D25" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>40</v>
+        <v>8000</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
           <t>581-KAM21BR71H104JT</t>
         </is>
+      </c>
+      <c r="C26" t="inlineStr"/>
+      <c r="D26" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>15</v>
+        <v>3000</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
           <t>581-KAF21BR72D102MT</t>
         </is>
+      </c>
+      <c r="C27" t="inlineStr"/>
+      <c r="D27" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>5</v>
+        <v>1000</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
           <t>791-0805N100J160CT</t>
         </is>
+      </c>
+      <c r="C28" t="inlineStr"/>
+      <c r="D28" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>20</v>
+        <v>4000</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
           <t>581-REF0511101M016K</t>
         </is>
+      </c>
+      <c r="C29" t="inlineStr"/>
+      <c r="D29" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>10</v>
+        <v>2000</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
           <t>80-ESK106M016AC3AA</t>
         </is>
+      </c>
+      <c r="C30" t="inlineStr"/>
+      <c r="D30" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>20</v>
+        <v>4000</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
           <t>80-ESK226M016AC3AA</t>
         </is>
+      </c>
+      <c r="C31" t="inlineStr"/>
+      <c r="D31" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>15</v>
+        <v>3000</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
           <t>696-SML-LXT0805GW</t>
         </is>
+      </c>
+      <c r="C32" t="inlineStr"/>
+      <c r="D32" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>10</v>
+        <v>2000</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
           <t>71-CRCW08053K90FHTAP</t>
         </is>
+      </c>
+      <c r="C33" t="inlineStr"/>
+      <c r="D33" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>10</v>
+        <v>2000</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
           <t>594-MCU0805MD2709DP5</t>
         </is>
+      </c>
+      <c r="C34" t="inlineStr"/>
+      <c r="D34" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>10</v>
+        <v>2000</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
           <t>78-1N4148WS-HE3-18</t>
         </is>
+      </c>
+      <c r="C35" t="inlineStr"/>
+      <c r="D35" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>5</v>
+        <v>1000</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
           <t>581-08056D475M</t>
         </is>
+      </c>
+      <c r="C36" t="inlineStr"/>
+      <c r="D36" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>10</v>
+        <v>2000</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
           <t>581-08053A4R7CAT2A</t>
         </is>
+      </c>
+      <c r="C37" t="inlineStr"/>
+      <c r="D37" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>10</v>
+        <v>2000</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
           <t>852-GP1S094HCZ0F</t>
         </is>
+      </c>
+      <c r="C38" t="inlineStr"/>
+      <c r="D38" t="n">
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -822,7 +982,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E39"/>
+  <dimension ref="A1:G39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -838,15 +998,25 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>PCB NUM</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>COMPONENTS PER PCB</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>Descripción</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Precio Unitario (€)</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Coste Total (€)</t>
         </is>
@@ -854,779 +1024,929 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>5</v>
+        <v>1000</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>71-CRCW0805-270-E3</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E2" t="inlineStr">
         <is>
           <t>Resistores de pel&amp;iacute;cula gruesa - SMD 1/8watt 270ohms 1% 100ppm</t>
         </is>
       </c>
-      <c r="D2" t="n">
-        <v>0.133</v>
-      </c>
-      <c r="E2" t="n">
-        <v>0.665</v>
+      <c r="F2" t="n">
+        <v>0.011</v>
+      </c>
+      <c r="G2" t="n">
+        <v>11</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>10</v>
+        <v>2000</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
           <t>71-RCS08051M00JNEA</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E3" t="inlineStr">
         <is>
           <t>Resistores de pel&amp;iacute;cula gruesa - SMD 500mW 1Mohms 5% 200ppm AEC-Q200</t>
         </is>
       </c>
-      <c r="D3" t="n">
-        <v>0.135</v>
-      </c>
-      <c r="E3" t="n">
-        <v>1.35</v>
+      <c r="F3" t="n">
+        <v>0.031</v>
+      </c>
+      <c r="G3" t="n">
+        <v>62</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>10</v>
+        <v>2000</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
           <t>71-CRCW0805100KJNECC</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E4" t="inlineStr">
         <is>
           <t>Resistores de pel&amp;iacute;cula gruesa - SMD 1/8Watt 100Kohms 5% Commercial Use</t>
         </is>
       </c>
-      <c r="D4" t="n">
-        <v>0.028</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0.28</v>
+      <c r="F4" t="n">
+        <v>0.008999999999999999</v>
+      </c>
+      <c r="G4" t="n">
+        <v>18</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>10</v>
+        <v>2000</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
           <t>71-CRCW0805-330-E3</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="n">
+        <v>2</v>
+      </c>
+      <c r="E5" t="inlineStr">
         <is>
           <t>Resistores de pel&amp;iacute;cula gruesa - SMD 1/8watt 330ohms 1% 100ppm</t>
         </is>
       </c>
-      <c r="D5" t="n">
-        <v>0.028</v>
-      </c>
-      <c r="E5" t="n">
-        <v>0.28</v>
+      <c r="F5" t="n">
+        <v>0.016</v>
+      </c>
+      <c r="G5" t="n">
+        <v>32</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>15</v>
+        <v>3000</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
           <t>71-CRCW080510R0FKEC</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="n">
+        <v>3</v>
+      </c>
+      <c r="E6" t="inlineStr">
         <is>
           <t>Resistores de pel&amp;iacute;cula gruesa - SMD D12/CRCW0805 100 10R 1% ET6 e3</t>
         </is>
       </c>
-      <c r="D6" t="n">
-        <v>0.024</v>
-      </c>
-      <c r="E6" t="n">
-        <v>0.36</v>
+      <c r="F6" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="G6" t="n">
+        <v>60</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>45</v>
+        <v>9000</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
           <t>71-CRCW0805103JT-RT6</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="n">
+        <v>9</v>
+      </c>
+      <c r="E7" t="inlineStr">
         <is>
           <t>Resistores de pel&amp;iacute;cula gruesa - SMD 1/8watt 10Kohms 5%</t>
         </is>
       </c>
-      <c r="D7" t="n">
-        <v>0.044</v>
-      </c>
-      <c r="E7" t="n">
-        <v>1.98</v>
+      <c r="F7" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="G7" t="n">
+        <v>189</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>35</v>
+        <v>7000</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
           <t>594-RCA08050000ZSEC</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="n">
+        <v>7</v>
+      </c>
+      <c r="E8" t="inlineStr">
         <is>
           <t>Resistores de pel&amp;iacute;cula gruesa - SMD RCA0805 0R0 ET6 E3</t>
         </is>
       </c>
-      <c r="D8" t="n">
-        <v>0.039</v>
-      </c>
-      <c r="E8" t="n">
-        <v>1.365</v>
+      <c r="F8" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="G8" t="n">
+        <v>84</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>5</v>
+        <v>1000</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
           <t>523-GSB4D313302Y1HR</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E9" t="inlineStr">
         <is>
           <t>Conectores USB USB4 GEN3 TYPEC CENT HEIGHT 1.58MM</t>
         </is>
       </c>
-      <c r="D9" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="E9" t="n">
-        <v>7.800000000000001</v>
+      <c r="F9" t="n">
+        <v>0.711</v>
+      </c>
+      <c r="G9" t="n">
+        <v>711</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>5</v>
+        <v>1000</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
           <t>926-LM1117IMPX33NOPB</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="n">
+        <v>1</v>
+      </c>
+      <c r="E10" t="inlineStr">
         <is>
           <t>Reguladores de voltaje LDO 800MA LDO LINEAR REG A 926-LM1117IMP3.3NOPB</t>
         </is>
       </c>
-      <c r="D10" t="n">
-        <v>0.96</v>
-      </c>
-      <c r="E10" t="n">
-        <v>4.8</v>
+      <c r="F10" t="n">
+        <v>0.463</v>
+      </c>
+      <c r="G10" t="n">
+        <v>463</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>5</v>
+        <v>1000</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
           <t>595-TPS63060DSCT</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="n">
+        <v>1</v>
+      </c>
+      <c r="E11" t="inlineStr">
         <is>
           <t>Reguladores de tensión de conmutación 2.5-12Vin 2.25A Sw C rnt Limit A 595-TPS63060DSCR</t>
         </is>
       </c>
-      <c r="D11" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="E11" t="n">
-        <v>13.5</v>
+      <c r="F11" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="G11" t="n">
+        <v>1430</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>5</v>
+        <v>1000</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
           <t>755-RB058L-30DDTE25</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="n">
+        <v>1</v>
+      </c>
+      <c r="E12" t="inlineStr">
         <is>
           <t>Diodos y rectificadores Schottky  SOT89  30V  3A  AUTO SCHOTTKY</t>
         </is>
       </c>
-      <c r="D12" t="n">
-        <v>0.751</v>
-      </c>
-      <c r="E12" t="n">
-        <v>3.755</v>
+      <c r="F12" t="n">
+        <v>0.257</v>
+      </c>
+      <c r="G12" t="n">
+        <v>257</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>5</v>
+        <v>1000</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
           <t>652-SRP6530A-1R0M</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E13" t="inlineStr">
         <is>
           <t>Inductores de potencia (SMD) Ind,7.1x6.6x3mm,1uH+/-20%,12A,shd</t>
         </is>
       </c>
-      <c r="D13" t="n">
-        <v>0.57</v>
-      </c>
-      <c r="E13" t="n">
-        <v>2.85</v>
+      <c r="F13" t="n">
+        <v>0.456</v>
+      </c>
+      <c r="G13" t="n">
+        <v>456</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>5</v>
+        <v>1000</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
           <t>852-PC817X4NSZ1B</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="n">
+        <v>1</v>
+      </c>
+      <c r="E14" t="inlineStr">
         <is>
           <t>Optoacopladores para salidas de transistores</t>
         </is>
       </c>
-      <c r="D14" t="n">
-        <v>0.665</v>
-      </c>
-      <c r="E14" t="n">
-        <v>3.325</v>
+      <c r="F14" t="n">
+        <v>0.223</v>
+      </c>
+      <c r="G14" t="n">
+        <v>223</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>5</v>
+        <v>1000</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
           <t>895-FT234XD-R</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="n">
+        <v>1</v>
+      </c>
+      <c r="E15" t="inlineStr">
         <is>
           <t>CI de interfaz USB USB to Serial UART Interface</t>
         </is>
       </c>
-      <c r="D15" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="E15" t="n">
-        <v>10.75</v>
+      <c r="F15" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="G15" t="n">
+        <v>1690</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>10</v>
+        <v>2000</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
           <t>70-ILSB0805ER1R0K</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="n">
+        <v>2</v>
+      </c>
+      <c r="E16" t="inlineStr">
         <is>
           <t>Inductores de RF (SMD) 1uH 10%</t>
         </is>
       </c>
-      <c r="D16" t="n">
-        <v>0.108</v>
-      </c>
-      <c r="E16" t="n">
-        <v>1.08</v>
+      <c r="F16" t="n">
+        <v>0.074</v>
+      </c>
+      <c r="G16" t="n">
+        <v>148</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>10</v>
+        <v>2000</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
           <t>595-TLV9062IDR</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="n">
+        <v>2</v>
+      </c>
+      <c r="E17" t="inlineStr">
         <is>
           <t>Amplificadores operacionales - Op Amps Dual 5.5-V 10-MHz operational amplifie</t>
         </is>
       </c>
-      <c r="D17" t="n">
-        <v>0.452</v>
-      </c>
-      <c r="E17" t="n">
-        <v>4.52</v>
+      <c r="F17" t="n">
+        <v>0.318</v>
+      </c>
+      <c r="G17" t="n">
+        <v>636</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>5</v>
+        <v>1000</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
           <t>179-SJ3-35094BG</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="n">
+        <v>1</v>
+      </c>
+      <c r="E18" t="inlineStr">
         <is>
           <t>Conectores de tel&amp;eacute;fono Audio Jack, 3.5mm, Through Hole, 4 Conductors, 2 Switches</t>
         </is>
       </c>
-      <c r="D18" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="E18" t="n">
-        <v>5.350000000000001</v>
+      <c r="F18" t="n">
+        <v>0.607</v>
+      </c>
+      <c r="G18" t="n">
+        <v>607</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>5</v>
+        <v>1000</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
           <t>356-ESP32WRVE26464PC</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="n">
+        <v>1</v>
+      </c>
+      <c r="E19" t="inlineStr">
         <is>
           <t>Módulos multiprotocolo SMD Module ESP32-WROVER-E, ESP32-D0WD-V3, 3.3V 64Mbit PSRAM, 8 MB SPI flash, PCB Antenna</t>
         </is>
       </c>
-      <c r="D19" t="n">
+      <c r="F19" t="n">
         <v>2.96</v>
       </c>
-      <c r="E19" t="n">
-        <v>14.8</v>
+      <c r="G19" t="n">
+        <v>2960</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>10</v>
+        <v>2000</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
           <t>583-BC817</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="C20" t="inlineStr"/>
+      <c r="D20" t="n">
+        <v>2</v>
+      </c>
+      <c r="E20" t="inlineStr">
         <is>
           <t>Transistores bipolares - BJT SOT23,NPN,0.8A,45V,G enPur</t>
         </is>
       </c>
-      <c r="D20" t="n">
-        <v>0.285</v>
-      </c>
-      <c r="E20" t="n">
-        <v>2.85</v>
+      <c r="F20" t="n">
+        <v>0.081</v>
+      </c>
+      <c r="G20" t="n">
+        <v>162</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>10</v>
+        <v>2000</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
           <t>583-BC807</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="C21" t="inlineStr"/>
+      <c r="D21" t="n">
+        <v>2</v>
+      </c>
+      <c r="E21" t="inlineStr">
         <is>
           <t>Transistores bipolares - BJT Gen Pur Trans PNP,0.8A,45V</t>
         </is>
       </c>
-      <c r="D21" t="n">
-        <v>0.266</v>
-      </c>
-      <c r="E21" t="n">
-        <v>2.66</v>
+      <c r="F21" t="n">
+        <v>0.076</v>
+      </c>
+      <c r="G21" t="n">
+        <v>152</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>5</v>
+        <v>1000</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
           <t>942-IRF3205ZPBF</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
+      <c r="C22" t="inlineStr"/>
+      <c r="D22" t="n">
+        <v>1</v>
+      </c>
+      <c r="E22" t="inlineStr">
         <is>
           <t>MOSFET MOSFT 55V 110A 6.5mOhm 76nC Qg</t>
         </is>
       </c>
-      <c r="D22" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="E22" t="n">
-        <v>6.600000000000001</v>
+      <c r="F22" t="n">
+        <v>0.659</v>
+      </c>
+      <c r="G22" t="n">
+        <v>659</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>10</v>
+        <v>2000</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
           <t>757-TTA006BQ</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
+      <c r="C23" t="inlineStr"/>
+      <c r="D23" t="n">
+        <v>2</v>
+      </c>
+      <c r="E23" t="inlineStr">
         <is>
           <t>Transistores bipolares - BJT Pb-F POWER TRANSISTOR TO-126N PC=10W F=1MHZ</t>
         </is>
       </c>
-      <c r="D23" t="n">
-        <v>0.619</v>
-      </c>
-      <c r="E23" t="n">
-        <v>6.19</v>
+      <c r="F23" t="n">
+        <v>0.337</v>
+      </c>
+      <c r="G23" t="n">
+        <v>674</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>10</v>
+        <v>2000</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
           <t>757-TTC011BQ</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
+      <c r="C24" t="inlineStr"/>
+      <c r="D24" t="n">
+        <v>2</v>
+      </c>
+      <c r="E24" t="inlineStr">
         <is>
           <t>Transistores bipolares - BJT Pb-FPOWERTRANSISTORTO-126NPC=10WF=1MHZ</t>
         </is>
       </c>
-      <c r="D24" t="n">
-        <v>0.655</v>
-      </c>
-      <c r="E24" t="n">
-        <v>6.550000000000001</v>
+      <c r="F24" t="n">
+        <v>0.318</v>
+      </c>
+      <c r="G24" t="n">
+        <v>636</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>30</v>
+        <v>6000</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
           <t>710-885342207014</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
+      <c r="C25" t="inlineStr"/>
+      <c r="D25" t="n">
+        <v>6</v>
+      </c>
+      <c r="E25" t="inlineStr">
         <is>
           <t>Condensadores de cerámica multicapa (MLCC- SMD/SMT) WCAP-CSMH 500V 0.01uF 0805 10%</t>
         </is>
       </c>
-      <c r="D25" t="n">
-        <v>0.067</v>
-      </c>
-      <c r="E25" t="n">
-        <v>2.01</v>
+      <c r="F25" t="n">
+        <v>0.046</v>
+      </c>
+      <c r="G25" t="n">
+        <v>276</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>40</v>
+        <v>8000</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
           <t>581-KAM21BR71H104JT</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
+      <c r="C26" t="inlineStr"/>
+      <c r="D26" t="n">
+        <v>8</v>
+      </c>
+      <c r="E26" t="inlineStr">
         <is>
           <t>Condensadores de cerámica multicapa (MLCC- SMD/SMT) 50V .1uF X7R 0805 5% AEC-Q200</t>
         </is>
       </c>
-      <c r="D26" t="n">
-        <v>0.121</v>
-      </c>
-      <c r="E26" t="n">
-        <v>4.84</v>
+      <c r="F26" t="n">
+        <v>0.033</v>
+      </c>
+      <c r="G26" t="n">
+        <v>264</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>15</v>
+        <v>3000</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
           <t>581-KAF21BR72D102MT</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
+      <c r="C27" t="inlineStr"/>
+      <c r="D27" t="n">
+        <v>3</v>
+      </c>
+      <c r="E27" t="inlineStr">
         <is>
           <t>Condensadores de cerámica multicapa (MLCC- SMD/SMT) 200V 1000pF X7R 0805 20% AEC-Q200 FLEXIT</t>
         </is>
       </c>
-      <c r="D27" t="n">
-        <v>0.068</v>
-      </c>
-      <c r="E27" t="n">
-        <v>1.02</v>
+      <c r="F27" t="n">
+        <v>0.029</v>
+      </c>
+      <c r="G27" t="n">
+        <v>87</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>5</v>
+        <v>1000</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
           <t>791-0805N100J160CT</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
+      <c r="C28" t="inlineStr"/>
+      <c r="D28" t="n">
+        <v>1</v>
+      </c>
+      <c r="E28" t="inlineStr">
         <is>
           <t>Condensadores de cerámica multicapa (MLCC- SMD/SMT) 10pF, +-5%, 16V</t>
         </is>
       </c>
-      <c r="D28" t="n">
-        <v>0.108</v>
-      </c>
-      <c r="E28" t="n">
-        <v>0.54</v>
+      <c r="F28" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="G28" t="n">
+        <v>12</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>20</v>
+        <v>4000</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
           <t>581-REF0511101M016K</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
+      <c r="C29" t="inlineStr"/>
+      <c r="D29" t="n">
+        <v>4</v>
+      </c>
+      <c r="E29" t="inlineStr">
         <is>
           <t>Condensadores electrolíticos de aluminio (con terminales radiales) ALUMINUM RADIAL</t>
         </is>
       </c>
-      <c r="D29" t="n">
-        <v>0.07099999999999999</v>
-      </c>
-      <c r="E29" t="n">
-        <v>1.42</v>
+      <c r="F29" t="n">
+        <v>0.045</v>
+      </c>
+      <c r="G29" t="n">
+        <v>180</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>10</v>
+        <v>2000</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
           <t>80-ESK106M016AC3AA</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
+      <c r="C30" t="inlineStr"/>
+      <c r="D30" t="n">
+        <v>2</v>
+      </c>
+      <c r="E30" t="inlineStr">
         <is>
           <t>Condensadores electrolíticos de aluminio (con terminales radiales) 16V 10uF 85C 2k Hour Radial</t>
         </is>
       </c>
-      <c r="D30" t="n">
-        <v>0.07099999999999999</v>
-      </c>
-      <c r="E30" t="n">
-        <v>0.71</v>
+      <c r="F30" t="n">
+        <v>0.045</v>
+      </c>
+      <c r="G30" t="n">
+        <v>90</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>20</v>
+        <v>4000</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
           <t>80-ESK226M016AC3AA</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
+      <c r="C31" t="inlineStr"/>
+      <c r="D31" t="n">
+        <v>4</v>
+      </c>
+      <c r="E31" t="inlineStr">
         <is>
           <t>Condensadores electrolíticos de aluminio (con terminales radiales) 16V 22uF 85C 2k Hour Radial</t>
         </is>
       </c>
-      <c r="D31" t="n">
-        <v>0.066</v>
-      </c>
-      <c r="E31" t="n">
-        <v>1.32</v>
+      <c r="F31" t="n">
+        <v>0.032</v>
+      </c>
+      <c r="G31" t="n">
+        <v>128</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>15</v>
+        <v>3000</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
           <t>696-SML-LXT0805GW</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr">
+      <c r="C32" t="inlineStr"/>
+      <c r="D32" t="n">
+        <v>3</v>
+      </c>
+      <c r="E32" t="inlineStr">
         <is>
           <t>LED de un solo color 0805 Thin PCB Green</t>
         </is>
       </c>
-      <c r="D32" t="n">
-        <v>0.132</v>
-      </c>
-      <c r="E32" t="n">
-        <v>1.98</v>
+      <c r="F32" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="G32" t="n">
+        <v>210</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>10</v>
+        <v>2000</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
           <t>71-CRCW08053K90FHTAP</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
+      <c r="C33" t="inlineStr"/>
+      <c r="D33" t="n">
+        <v>2</v>
+      </c>
+      <c r="E33" t="inlineStr">
         <is>
           <t>Resistores de pel&amp;iacute;cula gruesa - SMD CRCW0805-P 3.9K 1% 50 RT1</t>
         </is>
       </c>
-      <c r="D33" t="n">
-        <v>0.139</v>
-      </c>
-      <c r="E33" t="n">
-        <v>1.39</v>
+      <c r="F33" t="n">
+        <v>0.052</v>
+      </c>
+      <c r="G33" t="n">
+        <v>104</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>10</v>
+        <v>2000</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
           <t>594-MCU0805MD2709DP5</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
+      <c r="C34" t="inlineStr"/>
+      <c r="D34" t="n">
+        <v>2</v>
+      </c>
+      <c r="E34" t="inlineStr">
         <is>
           <t>Resistores de pel&amp;iacute;cula fina - SMD MCU 0805-25 0.5% AT P5 27R</t>
         </is>
       </c>
-      <c r="D34" t="n">
-        <v>0.208</v>
-      </c>
-      <c r="E34" t="n">
-        <v>2.08</v>
+      <c r="F34" t="n">
+        <v>0.094</v>
+      </c>
+      <c r="G34" t="n">
+        <v>188</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>10</v>
+        <v>2000</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
           <t>78-1N4148WS-HE3-18</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr">
+      <c r="C35" t="inlineStr"/>
+      <c r="D35" t="n">
+        <v>2</v>
+      </c>
+      <c r="E35" t="inlineStr">
         <is>
           <t>Diodos de conmutación de señal pequeña 100 Volt 350mA 4ns</t>
         </is>
       </c>
-      <c r="D35" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="E35" t="n">
-        <v>0.8999999999999999</v>
+      <c r="F35" t="n">
+        <v>0.034</v>
+      </c>
+      <c r="G35" t="n">
+        <v>68</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>5</v>
+        <v>1000</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
           <t>581-08056D475M</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr">
+      <c r="C36" t="inlineStr"/>
+      <c r="D36" t="n">
+        <v>1</v>
+      </c>
+      <c r="E36" t="inlineStr">
         <is>
           <t>Condensadores de cerámica multicapa (MLCC- SMD/SMT) KGM21AR50J475MU NEW GLOBAL PN 6.3V 4.7uF A 581-KGM21AR50J475MU</t>
         </is>
       </c>
-      <c r="D36" t="n">
-        <v>0.456</v>
-      </c>
-      <c r="E36" t="n">
-        <v>2.28</v>
+      <c r="F36" t="n">
+        <v>0.139</v>
+      </c>
+      <c r="G36" t="n">
+        <v>139</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>10</v>
+        <v>2000</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
           <t>581-08053A4R7CAT2A</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr">
+      <c r="C37" t="inlineStr"/>
+      <c r="D37" t="n">
+        <v>2</v>
+      </c>
+      <c r="E37" t="inlineStr">
         <is>
           <t>Condensadores de cerámica multicapa (MLCC- SMD/SMT) KGM21BCG1E4R7CT NEW GLOBAL PN 25V 4.7pF A 581-KGM21BCG1E4R7CT</t>
         </is>
       </c>
-      <c r="D37" t="n">
-        <v>0.121</v>
-      </c>
-      <c r="E37" t="n">
-        <v>1.21</v>
+      <c r="F37" t="n">
+        <v>0.049</v>
+      </c>
+      <c r="G37" t="n">
+        <v>98</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>10</v>
+        <v>2000</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
           <t>852-GP1S094HCZ0F</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr">
+      <c r="C38" t="inlineStr"/>
+      <c r="D38" t="n">
+        <v>2</v>
+      </c>
+      <c r="E38" t="inlineStr">
         <is>
           <t>Interruptores ópticos, transmisivos, con salida de fototransistor Photointerrupter 3.0mm gap</t>
         </is>
       </c>
-      <c r="D38" t="n">
-        <v>0.36</v>
-      </c>
-      <c r="E38" t="n">
-        <v>3.6</v>
+      <c r="F38" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="G38" t="n">
+        <v>580</v>
       </c>
     </row>
     <row r="39">
@@ -1638,8 +1958,10 @@
       </c>
       <c r="C39" t="inlineStr"/>
       <c r="D39" t="inlineStr"/>
-      <c r="E39" t="n">
-        <v>128.96</v>
+      <c r="E39" t="inlineStr"/>
+      <c r="F39" t="inlineStr"/>
+      <c r="G39" t="n">
+        <v>14744</v>
       </c>
     </row>
   </sheetData>
